--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.8401671287032</v>
+        <v>4.19902715841427</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72544456613818</v>
+        <v>4.017884741997454</v>
       </c>
       <c r="E2" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F2" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.75263698018884</v>
+        <v>4.997303509280687</v>
       </c>
       <c r="D3" t="n">
-        <v>29.69064375724177</v>
+        <v>4.824729610551787</v>
       </c>
       <c r="E3" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F3" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.23965989280392</v>
+        <v>4.426444732580638</v>
       </c>
       <c r="D4" t="n">
-        <v>26.10718566541899</v>
+        <v>4.242417670630586</v>
       </c>
       <c r="E4" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F4" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.19895583974548</v>
+        <v>3.607330323958641</v>
       </c>
       <c r="D5" t="n">
-        <v>21.78368091549993</v>
+        <v>3.539848148768739</v>
       </c>
       <c r="E5" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F5" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.71229778887955</v>
+        <v>2.065748390692926</v>
       </c>
       <c r="D6" t="n">
-        <v>11.77010091777695</v>
+        <v>1.912641399138755</v>
       </c>
       <c r="E6" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F6" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.13048753563269</v>
+        <v>4.408704224540312</v>
       </c>
       <c r="D7" t="n">
-        <v>27.09906483491545</v>
+        <v>4.40359803567376</v>
       </c>
       <c r="E7" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F7" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.67595010382831</v>
+        <v>3.3598418918721</v>
       </c>
       <c r="D8" t="n">
-        <v>20.18829368689767</v>
+        <v>3.280597724120871</v>
       </c>
       <c r="E8" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F8" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.22122665986741</v>
+        <v>1.985949332228455</v>
       </c>
       <c r="D9" t="n">
-        <v>12.43011363251716</v>
+        <v>2.019893465284039</v>
       </c>
       <c r="E9" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F9" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.609107350051749</v>
+        <v>0.5864799443834092</v>
       </c>
       <c r="D10" t="n">
-        <v>4.537214753864019</v>
+        <v>0.7372973975029031</v>
       </c>
       <c r="E10" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F10" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.25361437184961</v>
+        <v>3.616212335425562</v>
       </c>
       <c r="D11" t="n">
-        <v>22.6212155989781</v>
+        <v>3.675947534833942</v>
       </c>
       <c r="E11" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F11" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.9451811913466</v>
+        <v>3.078591943593822</v>
       </c>
       <c r="D12" t="n">
-        <v>19.18537939195643</v>
+        <v>3.11762415119292</v>
       </c>
       <c r="E12" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F12" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.37723886491226</v>
+        <v>5.098801315548242</v>
       </c>
       <c r="D13" t="n">
-        <v>32.29127162268163</v>
+        <v>5.247331638685765</v>
       </c>
       <c r="E13" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F13" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.55062336993324</v>
+        <v>5.126976297614153</v>
       </c>
       <c r="D14" t="n">
-        <v>32.66746918099017</v>
+        <v>5.308463741910902</v>
       </c>
       <c r="E14" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F14" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.19886790720321</v>
+        <v>8.644816034920522</v>
       </c>
       <c r="D15" t="n">
-        <v>52.00150099300095</v>
+        <v>8.450243911362653</v>
       </c>
       <c r="E15" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F15" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>18.21864324495839</v>
+        <v>2.960529527305738</v>
       </c>
       <c r="D16" t="n">
-        <v>19.4948470210857</v>
+        <v>3.167912640926426</v>
       </c>
       <c r="E16" t="n">
-        <v>10.92782510347312</v>
+        <v>1.775771579314382</v>
       </c>
       <c r="F16" t="n">
-        <v>10.64952785896513</v>
+        <v>1.730548277081834</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
